--- a/data/data_statics.xlsx
+++ b/data/data_statics.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1162,360 +1162,504 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>ele</t>
+          <t>ecdt</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>97</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1,498</t>
+          <t>137</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2,276</t>
+          <t>188</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>29,823</t>
+          <t>2,099</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>14,794</t>
+          <t>770</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>4,942</t>
+          <t>200</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hwu</t>
+          <t>ele</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>719</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>119</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1,498</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>2,276</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>379</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>7,712</t>
+          <t>29,823</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1,032</t>
+          <t>14,794</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>4,942</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>mcid</t>
+          <t>hwu</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>187</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>361</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>51</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>557</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>79</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1,198</t>
+          <t>7,712</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>1,032</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>933</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>64</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>mcid</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>94</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>1,198</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>331</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>170</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>539</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
           <t>stackoverflow</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>900</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>11,996</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>5,991</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>1,998</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>thucnews</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1,421</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>14</t>
         </is>
       </c>
     </row>
